--- a/光伏配储项目/电价数据/2026/曙光站.xlsx
+++ b/光伏配储项目/电价数据/2026/曙光站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50988</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.71512</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5641900000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51104</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.20898</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25505</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07436</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06116</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.04804</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.02818</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03879999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02673</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08601</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00554</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14513</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.20985</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.10878</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01074</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.18647</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.18456</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.21998</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.18011</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.11806</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.18783</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.03754</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.21494</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.43842</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52346</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.47199</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.75034</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61315</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.48635</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5740299999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.22167</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.4916</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.49587</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.60446</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.56048</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42903</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48432</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42908</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.61626</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.41761</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75225</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.10308</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.84765</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5441</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5269199999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51223</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50954</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47673</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52601</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6497999999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7464400000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44173</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44147</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08228000000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25756</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.24266</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5803700000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.13046</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27254</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.25448</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.56972</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.03166</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26849</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.2216</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15278</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.22511</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.24543</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.25231</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42844</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.24628</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.44216</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.25088</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7037899999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.89098</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.85795</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8373700000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.80326</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5970299999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43912</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43371</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.34011</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.53479</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47321</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47402</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.14555</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.44632</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06179999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.20767</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.13656</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.19563</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.18359</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24479</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.23032</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.19102</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.00101</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.2734</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.46575</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.49152</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34396</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47725</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26373</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19139</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10739</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.10813</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.07940999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21511</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.12221</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.20258</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06126</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00642</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.02638</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07411</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20702</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15724</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.20252</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.20665</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.23197</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25465</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47273</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29195</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04062</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04518</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03997</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04524</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04574</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04604999999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04722999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04638</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04759</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04618999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04752</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04878</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04844</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04618</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04724</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22008</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04661</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04935</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05201</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00221</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14697</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35133</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66426</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04195</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03228</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10687</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03746</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04690999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04128</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04143</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04134</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04386</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04379</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04125</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04067</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04051</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03912</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04417</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04122</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04007</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04271</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04651</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20219</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14468</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33762</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32254</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27338</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17423</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16049</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17311</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14948</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16119</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16056</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23939</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21599</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22858</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27183</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5312100000000001</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7910900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92001</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49429</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92715</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9042</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31796</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9272999999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63832</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22618</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88812</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5779099999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37095</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06044</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57104</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8251900000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.80738</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.8048099999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8918400000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.52528</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44115</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.24826</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5517300000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6627799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5485099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50947</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46083</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44438</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45189</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42222</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58951</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59681</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60192</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6468700000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.61748</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44721</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8645</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8299500000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.89735</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.88124</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8747200000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.45895</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27292</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35331</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.01826</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49732</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.49246</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41286</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.50178</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44174</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20107</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.49258</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.25295</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27504</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42887</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44715</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5977</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88975</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35624</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13728</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71099</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8047799999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65147</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5903200000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43764</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42835</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45078</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43444</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.82945</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.16461</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.68103</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23454</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6045499999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.8044600000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.49231</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.47767</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60377</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6902200000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46656</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32638</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.07088999999999999</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14623</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14885</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15578</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14472</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14472</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14356</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25868</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14533</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26833</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11468</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11365</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14235</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14759</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43841</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44168</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44111</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35059</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5974400000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47024</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42532</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20762</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44001</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36062</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43554</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26788</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03545</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25229</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2054</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18182</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24451</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25115</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49837</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.76689</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.44068</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45962</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.41916</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3083</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34971</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.70982</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6496900000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.86942</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4734</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34506</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13519</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19497</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24542</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12774</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.007549999999999999</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23575</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.02301</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14453</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.03868</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.22709</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23133</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6416900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6093200000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59212</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.4622</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.59727</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47575</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.71941</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48112</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49268</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45347</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41903</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56109</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5007900000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.26956</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.14441</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.02873</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.87126</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.13895</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.01137</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26207</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48524</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5061600000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50826</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.57702</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6698500000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.64258</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.63071</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7089800000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.51654</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50906</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7799400000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.72081</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5839299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6291100000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4700299999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46698</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46049</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5158200000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43587</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.26686</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03343</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45381</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46473</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18522</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36299</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24411</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23488</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23654</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24367</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25107</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03126</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.15954</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.26589</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.02984</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14779</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15249</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05218</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.00173</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24201</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35356</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19929</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.19127</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13503</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15578</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03568</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00167</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04722</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04165</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.05656</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19557</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22719</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22801</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2534</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24732</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23804</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.25472</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25839</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25925</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.26362</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.22515</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.22295</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.10312</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.02018</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.02468</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.17374</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.16866</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.16877</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.04693</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.24043</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17597</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16633</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.16748</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.19563</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.12099</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.13612</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19718</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.17167</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21703</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.19253</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17925</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22901</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.23056</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.23651</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21729</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.22309</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.14118</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.02317</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.22921</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.01113</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17906</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.17371</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.02655</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.0288</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.009220000000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.19096</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.03753</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.03897</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.09078</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04836</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.03023</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.03907</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.03841</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.02901</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23219</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.24971</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.17056</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32606</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10598</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.24495</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.10702</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.23455</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14975</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26978</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18421</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14387</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.09812</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33194</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24512</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.26594</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5689299999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.57159</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.24156</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26859</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28078</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.15232</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.25788</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26093</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24167</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.27764</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.45441</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.55863</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.5542</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.50992</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.00387</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.42233</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.45632</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5297200000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.46626</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.44531</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8523500000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.48819</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45241</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36901</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4660899999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.19523</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.16928</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23069</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25445</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.18851</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46261</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5580499999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5575399999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5503899999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49392</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53085</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5189199999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.71515</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7592899999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54762</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55018</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37661</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26658</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.25257</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23991</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25703</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.19264</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21515</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.12662</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.01584</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.15809</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01006</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.11137</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.02366</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01778</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02369</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.03571</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23487</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.02088</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02068</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03142</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01045</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02818</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06022</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11981</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16105</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22458</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18178</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.17884</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20959</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3803</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7485000000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27317</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26171</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22748</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19656</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.1966</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.20088</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21881</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.10284</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.009869999999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00936</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03627</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01311</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04467</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02189</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02938</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.21366</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04242</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.17808</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17231</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18935</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.13216</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.26613</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.18836</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22072</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18794</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.24369</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26554</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52739</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38681</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23562</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17625</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11531</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17963</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16774</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09068000000000001</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10817</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04672999999999999</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07326000000000001</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03503</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03589</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03637</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04593</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05356</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06088</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03609</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05809</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07421</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11854</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.15154</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16977</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.09231</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21761</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09406999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.19087</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.13457</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14329</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.17286</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.15064</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18564</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.20507</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20602</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21895</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25749</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.26153</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26318</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49624</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38248</v>
       </c>
     </row>
   </sheetData>
